--- a/public_administration_forms/014_youth_detention_feedback_survey--public_administration_forms.xlsx
+++ b/public_administration_forms/014_youth_detention_feedback_survey--public_administration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -765,8 +765,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -794,12 +794,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'counseling'}</t>
+          <t>counseling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Counseling'}</t>
+          <t>Counseling</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'education'}</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Education'}</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'recreational'}</t>
+          <t>recreational</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Recreational'}</t>
+          <t>Recreational</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'counseling'}</t>
+          <t>counseling</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Counseling'}</t>
+          <t>Counseling</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'education'}</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Education'}</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'recreational'}</t>
+          <t>recreational</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Recreational'}</t>
+          <t>Recreational</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
